--- a/scenarios/S04_sap_copa_report/deliverables/계정매핑_퍼널단계_시트.xlsx
+++ b/scenarios/S04_sap_copa_report/deliverables/계정매핑_퍼널단계_시트.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계정매핑" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="퍼널단계정의" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="리포트항목" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -858,4 +859,372 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>req_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>요청자</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>영향 산출물</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>변경유형</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DA점수</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>위키 커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-20260725-marketing-funnel-copa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:55:31.472+09:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>경영관리 김PM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bench:S04:B00000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>진행을 승인하고 CO-PA 리포트, Marketing Funnel 손익계산서 설계서, 단계별 기여손익 로직·테스트 시나리오를 갱신한다. 퍼널 단계, 공통 판관비 배부, 기존 CO-PA 대사, 데이터 완전성·권한·컴플라이언스 기준은 후속 확정한다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Marketing Funnel 단계별 매출·비용·기여손익과 CO-PA 매핑 및 판관비 배부 기준을 반영한다.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CO-PA 리포트 구조 정의서; Marketing Funnel 손익계산서 설계서; 단계별 기여손익 산출 로직 및 테스트 시나리오</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/0895639a7f55226b6290110ec86338315d8fa5be</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-20260725-marketing-funnel-copa-approval-confirmed</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:12:45.254+09:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>경영관리 김PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bench:S04:B00001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>승인 페이로드에 따라 CO-PA 리포트 및 관련 설계서·추적표·경영 보고 장장의 갱신을 승인 완료로 기록하며, 단계 정의·공통비 배부·손익 대사·데이터 계보·권한 및 컴플라이언스 기준은 후속 확정 과제로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CO-PA 리포트를 Marketing Funnel 기반 단계별·누적 기여손익 구조로 개편하기 위한 설계 및 관련 산출물 갱신 범위를 정의했으며, 단계 정의·공통비 배부·대사·통제 기준은 확인이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CO-PA 리포트 구조 정의서; Marketing Funnel 손익계산서 설계서; 단계별 기여손익 산출 로직 및 테스트 시나리오; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/220405aed990829201503ed1b927599965bb7b99</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20260725-marketing-funnel-copa-approval-confirmed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:09:51.896+09:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>경영관리 김PM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bench:S04:B00010</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CO-PA 리포트 및 관련 산출물의 갱신 완료를 승인하고, 단계 정의·공통비 배부·대사·데이터 품질·권한·감사통제 기준은 후속 확정 과제로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CO-PA 리포트를 인지·고려·전환 단계별 매출·원가·직접비·공통비·기여손익 구조로 개편하고 설계서·추적표·경영 보고 장표를 갱신한다.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CO-PA 리포트 구조 정의서; Marketing Funnel 손익계산서 설계서; 단계별 기여손익 산출 로직 및 테스트 시나리오; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx; LLM Wiki 및 GitHub 기록</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/5c4bf0464eb8d39c56e55bbfcb6496a76e94b90c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-20260725-marketing-funnel-copa-approval-execution</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-31T14:07:11.929Z</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>경영관리 김PM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bench:S04:B00100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CO-PA 리포트 개편 및 관련 설계서·추적표·경영 보고 장표 갱신을 승인하고, 단계 정의·비용 배부·대사·데이터·권한·컴플라이언스 기준은 후속 확정 과제로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>승인 페이로드에 따라 Marketing Funnel 단계별 CO-PA 기여손익 구조와 관련 산출물 갱신 결과를 승인 상태로 기록한다.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CO-PA 리포트 구조 정의서; Marketing Funnel 손익계산서 설계서; 단계별 기여손익 산출 로직 및 테스트 시나리오; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>modify; add; add; modify; modify; modify</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/dcf27687957235fa832d4ecce9af2b7211f346a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-20260725-marketing-funnel-copa-execution</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:02:59.066+09:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>경영관리 김PM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bench:S04:B01000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Marketing Funnel 단계별 손익 구조, 직접비·공통 판관비 구분 및 배부, 단계별·누적 기여손익, CO-PA 매핑·대사·검증 기준을 승인하고 관련 산출물 갱신을 진행한다. 단계 정의, 배부 기준, 대사 허용오차, 권한·컴플라이언스 및 cross-module 인터페이스의 세부 기준은 후속 확정 과제로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SAP CO-PA 손익계산서를 인지·고려·전환의 Marketing Funnel 단계별 구조로 개편하고 매출·매출원가·직접비·공통 판관비, 단계별·누적 기여손익, CO-PA 매핑·대사·검증 기준을 반영한다.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CO-PA 리포트 구조 정의서; Marketing Funnel 손익계산서 설계서; 단계별 기여손익 산출 로직 및 테스트 시나리오; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/5c7c903f380e1adc55fb94dfd9b6288da8dc6d6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-20260725-marketing-funnel-copa-execution</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:58:39.407+09:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>경영관리 김PM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bench:S04:B10000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DA 검토(score 5)에 따라 산출물 갱신을 진행·완료한 것으로 승인하며, 퍼널 단계·공통비 배부·대사 허용오차·데이터 거버넌스·권한 및 컴플라이언스 기준은 후속 확정 과제로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CO-PA를 Marketing Funnel 단계별 기여손익 구조로 재설계하고, 판관비 배부·대사·권한 기준 확정을 후속 과제로 관리합니다.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CO-PA 리포트 구조 정의서; Marketing Funnel 손익계산서 설계서; 단계별 기여손익 산출 로직 및 테스트 시나리오; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/5a96220adfdb184ec8e07de530097d9b55a9741e</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>